--- a/outputs/security-lab-matrix/amr-fitness-vulnerability-matrix.xlsx
+++ b/outputs/security-lab-matrix/amr-fitness-vulnerability-matrix.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerability Matrix" sheetId="1" r:id="Re11e6b5024664062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerability Matrix" sheetId="1" r:id="Ra66fe3bd68a34a7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Test Data" sheetId="2" r:id="Rd8fc37ec3eb04983"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,6 +47,12 @@
       <x:i/>
       <x:sz val="11"/>
       <x:color rgb="FF334155"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -173,7 +180,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -293,6 +300,16 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -745,9 +762,9 @@
         <x:v>A01:2021 Broken Access Control</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
-        <x:v>1. Log in as Member 1 (member@amrfitness.local, MEM-10001).
-2. Submit GET /api/member/activity?memberId=MEM-10002 or /profile?memberId=MEM-10002.
-3. Verify API returns Member MEM-10002's private data without ownership check.</x:v>
+        <x:v>1. Log in as Member 1 (member@amrfitness.local, kmc-143).
+2. Submit GET /api/member/profile?memberId=kmc-144 or PUT /api/member/profile?memberId=kmc-144.
+3. Verify API returns Member kmc-144's private data and updates profile without ownership check.</x:v>
       </x:c>
       <x:c r="E11" s="37" t="str">
         <x:v>Unauthorized exposure of private workout and health data
@@ -814,28 +831,28 @@
     </x:row>
     <x:row r="14" ht="76" customHeight="1">
       <x:c r="A14" s="43" t="str">
-        <x:v>Known CVE components</x:v>
+        <x:v>Verbose error messages &amp; stack trace leakage</x:v>
       </x:c>
       <x:c r="B14" s="46" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="C14" s="37" t="str">
-        <x:v>A06:2021 Vulnerable &amp; Outdated Components</x:v>
+        <x:v>A05:2021 Security Misconfiguration</x:v>
       </x:c>
       <x:c r="D14" s="37" t="str">
-        <x:v>1. Inspect package.json dependency declarations.
-2. Run npm audit or dependency vulnerability scanners.
-3. Verify pinned legacy dependencies (lodash@4.17.15, qs@6.7.0, jsonwebtoken@8.5.1) exhibit public CVEs.</x:v>
+        <x:v>1. Send request to GET /api/system/debug/error or click System Diagnostics in footer.
+2. Inspect API response HTTP status (500 Internal Server Error) and JSON payload.
+3. Verify server leaks raw Node.js stack traces, file system paths, and internal error codes.</x:v>
       </x:c>
       <x:c r="E14" s="37" t="str">
-        <x:v>Known exploit exposure via unpatched CVEs
-Transitive prototype pollution vulnerabilities
-Compliance and audit audit failures</x:v>
+        <x:v>System internal file path and environment disclosure
+Facilitates precise targeted exploit payload creation
+Exposes internal application architecture to attackers</x:v>
       </x:c>
       <x:c r="F14" s="38" t="str">
-        <x:v>Update dependencies to supported non-vulnerable releases
-Automate dependency vulnerability scanning (SCA/SBOM)
-Enforce patching SLAs</x:v>
+        <x:v>Generic error responses in production environments
+Log detailed stack traces to secure server-side logging systems
+Disable verbose error middleware in production builds</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="76" customHeight="1">
@@ -849,20 +866,20 @@
         <x:v>A05:2021 Security Misconfiguration</x:v>
       </x:c>
       <x:c r="D15" s="37" t="str">
-        <x:v>1. Search compiled JS bundle in dist/client/assets/ for AMR_SECRET_MASTER_API_KEY.
-2. Locate AMR_SECRET_MASTER_API_KEY_2026_V1 in client bundle.
-3. Submit GET /api/admin/dashboard with header "x-admin-key: AMR_SECRET_MASTER_API_KEY_2026_V1".
-4. Verify server grants full admin access without authentication.</x:v>
+        <x:v>1. Open browser DevTools (F12) -&gt; Sources tab or inspect loaded JS bundle (assets/index-*.js) in Burp Suite.
+2. Search JS assets for API key references to find AMR_SECRET_MASTER_API_KEY_2026_V1.
+3. Send HTTP request to GET /api/admin/dashboard with header "x-admin-key: AMR_SECRET_MASTER_API_KEY_2026_V1".
+4. Verify backend grants full administrative privileges without authenticating.</x:v>
       </x:c>
       <x:c r="E15" s="37" t="str">
-        <x:v>Complete system and administrative takeover
-Bypasses standard authentication and role checks
-Permanent compromise as long as secret is in client bundle</x:v>
+        <x:v>Complete administrative takeover of the application
+Bypasses standard authentication and session controls
+Permanent backdoor exposure while secret exists in client build assets</x:v>
       </x:c>
       <x:c r="F15" s="38" t="str">
-        <x:v>Zero secret client bundles (never embed master keys)
-Server-side authorization only
-Automated secret scanning (GitGuardian/TruffleHog) in CI/CD</x:v>
+        <x:v>Never embed administrative API keys or master secrets in client-side code
+Implement strict server-side authentication and session authorization
+Enforce automated secret scanning (GitGuardian/TruffleHog) in build pipelines</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="76" customHeight="1">
@@ -904,8 +921,8 @@
       </x:c>
       <x:c r="D17" s="37" t="str">
         <x:v>1. Submit POST /api/auth/forgot-password with target email.
-2. Observe resetToken returned: MD5(email).
-3. Submit POST /api/auth/reset-password-with-token using forged token MD5(target_email).
+2. Intercept response to observe resetToken: MD5(email).
+3. Submit POST /api/auth/reset-password-with-token using token MD5(target_email).
 4. Verify target account password is reset via forged token.</x:v>
       </x:c>
       <x:c r="E17" s="37" t="str">
@@ -995,4 +1012,403 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="54" t="str">
+        <x:v>AMR Fitness — Sample Working Test Data &amp; Exploit Vectors</x:v>
+      </x:c>
+      <x:c r="B1" s="54"/>
+      <x:c r="C1" s="54"/>
+      <x:c r="D1" s="54"/>
+      <x:c r="E1" s="54"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="55" t="str">
+        <x:v>Account Type</x:v>
+      </x:c>
+      <x:c r="B3" s="55" t="str">
+        <x:v>Email Address</x:v>
+      </x:c>
+      <x:c r="C3" s="55" t="str">
+        <x:v>Password</x:v>
+      </x:c>
+      <x:c r="D3" s="55" t="str">
+        <x:v>Member ID / Role</x:v>
+      </x:c>
+      <x:c r="E3" s="55" t="str">
+        <x:v>Notes / Context</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Admin Account</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>admin@amrfitness.local</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>AMR#Fitness$2026!AdminKey</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Role: admin</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>Primary lead administrator account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Primary Member</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>member@amrfitness.local</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Member@12345</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>kmc-143 / role: member</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>Primary student member test account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Secondary Member</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>priya.s@example.com</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Fitness@123</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>kmc-144 / role: member</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>Target member for IDOR testing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Tertiary Member</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>ananya.v@example.com</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Fitness@123</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>kmc-145 / role: member</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Target member for IDOR testing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str"/>
+      <x:c r="B8" t="str"/>
+      <x:c r="C8" t="str"/>
+      <x:c r="D8" t="str"/>
+      <x:c r="E8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="55" t="str">
+        <x:v>Payment Category</x:v>
+      </x:c>
+      <x:c r="B9" s="55" t="str">
+        <x:v>Field Name</x:v>
+      </x:c>
+      <x:c r="C9" s="55" t="str">
+        <x:v>Sample Test Value</x:v>
+      </x:c>
+      <x:c r="D9" s="55" t="str">
+        <x:v>Format / Type</x:v>
+      </x:c>
+      <x:c r="E9" s="55" t="str">
+        <x:v>Usage Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Cardholder Name</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Rahul Sharma</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Cardholder name input</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Card Number</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>4532 8912 3456 7890</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>16-digit formatted</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Simulated Visa/Mastercard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Expiry Date</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>12/28</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>MM/YY</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Future expiration date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Credit / Debit Card</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>CVV Code</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>3 digits</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Security code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>UPI / Mobile</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Virtual Payment Address</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>rahul@okicici</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>VPA string</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Sample ICICI UPI ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>UPI / Mobile</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Secondary VPA</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>member@paytm</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>VPA string</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Sample Paytm UPI ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Net Banking</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Primary Bank Name</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>HDFC Bank NetBanking</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Select Option</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>HDFC Bank option</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Net Banking</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Customer ID</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>HDFC_USER_9941</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Text ID</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Customer User ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="55" t="str"/>
+      <x:c r="B18" s="55" t="str"/>
+      <x:c r="C18" s="55" t="str"/>
+      <x:c r="D18" s="55" t="str"/>
+      <x:c r="E18" s="55" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Vulnerability Vectors</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Parameter / Header</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Sample Exploit Payload</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Target Endpoint</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Hardcoded Master Key</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>x-admin-key header</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>AMR_SECRET_MASTER_API_KEY_2026_V1</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>GET /api/admin/dashboard</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Bypasses auth; grants admin session</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>IDOR Profile Access</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>memberId query param</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>kmc-144</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>GET /api/member/profile?memberId=kmc-144</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Returns target member private profile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>IDOR Profile Edit</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>memberId parameter</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>kmc-144</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>PUT /api/member/profile?memberId=kmc-144</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Updates target member profile details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>Predictable Reset Token</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>resetToken parameter</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>MD5(target_email)</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>POST /api/auth/reset-password-with-token</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Resets target user password via forged token</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>Subscription Price Bypass</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>pricePaise body param</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>POST /api/membership/subscribe</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Activates Elite plan for ₹0 charged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>Mass Assignment Role</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>role body param</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>admin</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>PUT /api/member/profile</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Escalates member role to admin</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>